--- a/artfynd/A 20935-2026 artfynd.xlsx
+++ b/artfynd/A 20935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97157902</v>
+        <v>134430634</v>
       </c>
       <c r="B2" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkasjö , Hl</t>
+          <t>Flathult, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353905.94385728</v>
+        <v>353269</v>
       </c>
       <c r="R2" t="n">
-        <v>6330167.632454661</v>
+        <v>6330367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,15 +770,128 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97157902</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75910</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björkasjö , Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>353905.94385728</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6330167.632454661</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Ida Johansson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Ida Johansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20935-2026 artfynd.xlsx
+++ b/artfynd/A 20935-2026 artfynd.xlsx
@@ -675,45 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134430634</v>
+        <v>97157902</v>
       </c>
       <c r="B2" t="n">
-        <v>96505</v>
+        <v>77726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flathult, Hl</t>
+          <t>Björkasjö , Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353269</v>
+        <v>353907</v>
       </c>
       <c r="R2" t="n">
-        <v>6330367</v>
+        <v>6330168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,63 +761,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97157902</v>
+        <v>134430353</v>
       </c>
       <c r="B3" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkasjö , Hl</t>
+          <t>Flathult, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353905.94385728</v>
+        <v>353269</v>
       </c>
       <c r="R3" t="n">
-        <v>6330167.632454661</v>
+        <v>6330367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,22 +838,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,12 +868,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 20935-2026 artfynd.xlsx
+++ b/artfynd/A 20935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134799770</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96512</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogshagen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>353531</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6330364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20935-2026 artfynd.xlsx
+++ b/artfynd/A 20935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134430353</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134799770</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>